--- a/data/trans_orig/P57B4_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57B4_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha tenido la sensación de disfrutar de la vida en 2023</t>
+          <t>Población según si ha tenido la sensación de disfrutar de la vida en 2023 (tasa de respuesta: 99,21%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>233976</t>
+          <t>235650</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>292913</t>
+          <t>291122</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>201037</t>
+          <t>199789</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>241434</t>
+          <t>241145</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>445324</t>
+          <t>446536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>519042</t>
+          <t>518543</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>226328</t>
+          <t>226732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277803</t>
+          <t>278677</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289858</t>
+          <t>288267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>329246</t>
+          <t>329172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>528424</t>
+          <t>529695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>597005</t>
+          <t>595228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81980</t>
+          <t>81385</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117675</t>
+          <t>115447</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>94706</t>
+          <t>96040</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>122742</t>
+          <t>123847</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>185390</t>
+          <t>184719</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>229415</t>
+          <t>230022</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13816</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>30324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19179</t>
+          <t>18956</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33600</t>
+          <t>34721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37007</t>
+          <t>37133</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58640</t>
+          <t>60525</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518190</t>
+          <t>516768</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>890258</t>
+          <t>949894</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>324082</t>
+          <t>322582</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>376962</t>
+          <t>377490</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>859322</t>
+          <t>857368</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1385359</t>
+          <t>1383447</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,61%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>230276</t>
+          <t>175856</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>517392</t>
+          <t>517644</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>398319</t>
+          <t>398902</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>453427</t>
+          <t>451101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>549641</t>
+          <t>565900</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>946313</t>
+          <t>950140</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52065</t>
+          <t>46503</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128560</t>
+          <t>126170</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132927</t>
+          <t>133032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>170229</t>
+          <t>169751</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167434</t>
+          <t>160296</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>285103</t>
+          <t>284576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59826</t>
+          <t>56372</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19850</t>
+          <t>19725</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36964</t>
+          <t>38250</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>34017</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81354</t>
+          <t>83915</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>299035</t>
+          <t>297982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>360349</t>
+          <t>362260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>327288</t>
+          <t>329436</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>685177</t>
+          <t>709940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>667114</t>
+          <t>665255</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1084106</t>
+          <t>1096551</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>67,31%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>265796</t>
+          <t>265490</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>325574</t>
+          <t>328346</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>193062</t>
+          <t>179191</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>496078</t>
+          <t>492996</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>425361</t>
+          <t>428833</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>782675</t>
+          <t>783738</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,11%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46009</t>
+          <t>46047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79841</t>
+          <t>79057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32410</t>
+          <t>32576</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89285</t>
+          <t>91440</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77325</t>
+          <t>79118</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154794</t>
+          <t>155457</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22868</t>
+          <t>23002</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>8529</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31338</t>
+          <t>30444</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21455</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46487</t>
+          <t>47342</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>336048</t>
+          <t>334903</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>401708</t>
+          <t>401055</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>282654</t>
+          <t>277170</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>388939</t>
+          <t>385646</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>635051</t>
+          <t>632854</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>764355</t>
+          <t>764569</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>374276</t>
+          <t>371059</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>436345</t>
+          <t>436425</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>469428</t>
+          <t>471909</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>629390</t>
+          <t>629490</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>868047</t>
+          <t>871461</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1055168</t>
+          <t>1053716</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,44%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>111444</t>
+          <t>111789</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>153038</t>
+          <t>154605</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>148303</t>
+          <t>149863</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>212133</t>
+          <t>212092</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>279934</t>
+          <t>274334</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>351511</t>
+          <t>350333</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25189</t>
+          <t>24217</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25107</t>
+          <t>24520</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45012</t>
+          <t>44148</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39192</t>
+          <t>39452</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63160</t>
+          <t>63363</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1468868</t>
+          <t>1460564</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2056842</t>
+          <t>1982501</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1228477</t>
+          <t>1228341</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1847207</t>
+          <t>1774694</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2753967</t>
+          <t>2735154</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3622464</t>
+          <t>3545440</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>50,09%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1029513</t>
+          <t>1090708</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1477263</t>
+          <t>1486636</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1315468</t>
+          <t>1338771</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1766227</t>
+          <t>1768763</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2545387</t>
+          <t>2601003</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3189077</t>
+          <t>3199985</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>296750</t>
+          <t>304242</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>432869</t>
+          <t>431791</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>413900</t>
+          <t>422031</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>562106</t>
+          <t>563810</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>766629</t>
+          <t>773080</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>964875</t>
+          <t>972187</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>57405</t>
+          <t>57652</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>108991</t>
+          <t>109672</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>85539</t>
+          <t>85084</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>125495</t>
+          <t>127549</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>153767</t>
+          <t>155875</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>218549</t>
+          <t>224266</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B4_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57B4_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>261244</t>
+          <t>281013</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>235650</t>
+          <t>251720</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>291122</t>
+          <t>309393</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>220615</t>
+          <t>241777</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>199789</t>
+          <t>221082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>241145</t>
+          <t>266596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>481858</t>
+          <t>522790</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>446536</t>
+          <t>489027</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>518543</t>
+          <t>562518</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>253316</t>
+          <t>280282</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>226732</t>
+          <t>253843</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278677</t>
+          <t>307180</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>309502</t>
+          <t>336091</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>288267</t>
+          <t>311924</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>329172</t>
+          <t>358571</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>562818</t>
+          <t>616373</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>529695</t>
+          <t>579030</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>595228</t>
+          <t>651553</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97982</t>
+          <t>105079</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81385</t>
+          <t>87756</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115447</t>
+          <t>125732</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>108592</t>
+          <t>115807</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>96040</t>
+          <t>102683</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>123847</t>
+          <t>131638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>206575</t>
+          <t>220885</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>184719</t>
+          <t>198648</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>230022</t>
+          <t>244886</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21401</t>
+          <t>22782</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>14913</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30324</t>
+          <t>32734</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25923</t>
+          <t>27735</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34721</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>47324</t>
+          <t>50516</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37133</t>
+          <t>39757</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60525</t>
+          <t>63133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>633943</t>
+          <t>689156</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>633943</t>
+          <t>689156</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>633943</t>
+          <t>689156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>664632</t>
+          <t>721409</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>664632</t>
+          <t>721409</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>664632</t>
+          <t>721409</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1298575</t>
+          <t>1410565</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1298575</t>
+          <t>1410565</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1298575</t>
+          <t>1410565</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>666898</t>
+          <t>469016</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>516768</t>
+          <t>430408</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>949894</t>
+          <t>506147</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>350189</t>
+          <t>389873</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>322582</t>
+          <t>360391</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>377490</t>
+          <t>417851</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1017087</t>
+          <t>858890</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>857368</t>
+          <t>813013</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1383447</t>
+          <t>903476</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>401358</t>
+          <t>448836</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>175856</t>
+          <t>412719</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>517644</t>
+          <t>486222</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>425090</t>
+          <t>478049</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>398902</t>
+          <t>449793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>451101</t>
+          <t>505915</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>826448</t>
+          <t>926885</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>565900</t>
+          <t>884862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>950140</t>
+          <t>975647</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95011</t>
+          <t>106208</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46503</t>
+          <t>87133</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126170</t>
+          <t>126949</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>149377</t>
+          <t>167582</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133032</t>
+          <t>149340</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>169751</t>
+          <t>189140</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>244388</t>
+          <t>273790</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160296</t>
+          <t>246661</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>284576</t>
+          <t>300985</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26158</t>
+          <t>21046</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10978</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56372</t>
+          <t>33672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27311</t>
+          <t>28535</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19725</t>
+          <t>21056</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38250</t>
+          <t>39431</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>53469</t>
+          <t>49581</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34017</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83915</t>
+          <t>64198</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1189424</t>
+          <t>1045106</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1189424</t>
+          <t>1045106</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1189424</t>
+          <t>1045106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>951968</t>
+          <t>1064039</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>951968</t>
+          <t>1064039</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>951968</t>
+          <t>1064039</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2141392</t>
+          <t>2109145</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2141392</t>
+          <t>2109145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2141392</t>
+          <t>2109145</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>330595</t>
+          <t>366300</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>297982</t>
+          <t>335132</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>362260</t>
+          <t>400029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>472927</t>
+          <t>312965</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>329436</t>
+          <t>286202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>709940</t>
+          <t>342364</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>803522</t>
+          <t>679264</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>665255</t>
+          <t>639934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1096551</t>
+          <t>719601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>295190</t>
+          <t>337998</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>265490</t>
+          <t>306487</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>328346</t>
+          <t>369595</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>371444</t>
+          <t>392901</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>179191</t>
+          <t>366700</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>492996</t>
+          <t>420135</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>666634</t>
+          <t>730899</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428833</t>
+          <t>686352</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>783738</t>
+          <t>768442</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,0%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>60753</t>
+          <t>72684</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46047</t>
+          <t>55316</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79057</t>
+          <t>91981</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>64494</t>
+          <t>79535</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32576</t>
+          <t>64389</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91440</t>
+          <t>97112</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>125246</t>
+          <t>152219</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79118</t>
+          <t>129625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155457</t>
+          <t>180736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>16969</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23002</t>
+          <t>27033</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19704</t>
+          <t>21662</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8529</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30444</t>
+          <t>30393</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>33795</t>
+          <t>38632</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21553</t>
+          <t>27981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47342</t>
+          <t>50983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>700629</t>
+          <t>793951</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>700629</t>
+          <t>793951</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>700629</t>
+          <t>793951</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>928569</t>
+          <t>807063</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>928569</t>
+          <t>807063</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>928569</t>
+          <t>807063</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1629197</t>
+          <t>1601014</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1629197</t>
+          <t>1601014</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1629197</t>
+          <t>1601014</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>368552</t>
+          <t>396715</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>334903</t>
+          <t>362467</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>401055</t>
+          <t>428229</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>348365</t>
+          <t>387213</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>277170</t>
+          <t>358289</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>385646</t>
+          <t>416404</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>716916</t>
+          <t>783928</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>632854</t>
+          <t>739896</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>764569</t>
+          <t>830132</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>405043</t>
+          <t>427344</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>371059</t>
+          <t>396494</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>436425</t>
+          <t>462458</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>520312</t>
+          <t>486872</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>471909</t>
+          <t>456034</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>629490</t>
+          <t>516384</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>925354</t>
+          <t>914216</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>871461</t>
+          <t>865876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1053716</t>
+          <t>957366</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>131032</t>
+          <t>142183</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>111789</t>
+          <t>121483</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>154605</t>
+          <t>165428</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>186188</t>
+          <t>199595</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>149863</t>
+          <t>179969</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>212092</t>
+          <t>222512</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>317220</t>
+          <t>341778</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>274334</t>
+          <t>311403</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>350333</t>
+          <t>371784</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>16317</t>
+          <t>18222</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>11563</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24217</t>
+          <t>27856</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>33679</t>
+          <t>37754</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24520</t>
+          <t>28020</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44148</t>
+          <t>48818</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>49995</t>
+          <t>55977</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39452</t>
+          <t>43078</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63363</t>
+          <t>69957</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>920944</t>
+          <t>984465</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>920944</t>
+          <t>984465</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>920944</t>
+          <t>984465</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1088543</t>
+          <t>1111434</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1088543</t>
+          <t>1111434</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1088543</t>
+          <t>1111434</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2009486</t>
+          <t>2095899</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2009486</t>
+          <t>2095899</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2009486</t>
+          <t>2095899</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1627288</t>
+          <t>1513044</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1460564</t>
+          <t>1446631</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1982501</t>
+          <t>1583281</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1392096</t>
+          <t>1331827</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1228341</t>
+          <t>1278789</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1774694</t>
+          <t>1383064</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3019384</t>
+          <t>2844872</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2735154</t>
+          <t>2763340</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3545440</t>
+          <t>2936468</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1354907</t>
+          <t>1494460</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1090708</t>
+          <t>1428390</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1486636</t>
+          <t>1556661</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1626348</t>
+          <t>1693913</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1338771</t>
+          <t>1641064</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1768763</t>
+          <t>1742774</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2981254</t>
+          <t>3188373</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2601003</t>
+          <t>3100265</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3199985</t>
+          <t>3268935</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,3%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>384778</t>
+          <t>426154</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>304242</t>
+          <t>386282</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>431791</t>
+          <t>465187</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>508651</t>
+          <t>562520</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>422031</t>
+          <t>526464</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>563810</t>
+          <t>597818</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>893429</t>
+          <t>988673</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>773080</t>
+          <t>931602</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>972187</t>
+          <t>1042631</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>77966</t>
+          <t>79019</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>57652</t>
+          <t>62133</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>109672</t>
+          <t>97436</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>106617</t>
+          <t>115686</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>85084</t>
+          <t>97730</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>127549</t>
+          <t>132065</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>184584</t>
+          <t>194705</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>155875</t>
+          <t>173174</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>224266</t>
+          <t>222563</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3444939</t>
+          <t>3512677</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3444939</t>
+          <t>3512677</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3444939</t>
+          <t>3512677</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3633712</t>
+          <t>3703946</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3633712</t>
+          <t>3703946</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3633712</t>
+          <t>3703946</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7078651</t>
+          <t>7216623</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7078651</t>
+          <t>7216623</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7078651</t>
+          <t>7216623</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
